--- a/technology.xlsx
+++ b/technology.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hy4174/Documents/GitHub/GCAM_USA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2753F62C-66A0-F945-9113-DAEBB2B19682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F7E3D4-4064-3B47-98BC-4FD8A68C33D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="760" windowWidth="24320" windowHeight="20520" activeTab="7" xr2:uid="{05EA3646-A85E-534D-A1FC-571F8F5FDE62}"/>
+    <workbookView xWindow="26880" yWindow="4400" windowWidth="24320" windowHeight="20520" activeTab="5" xr2:uid="{05EA3646-A85E-534D-A1FC-571F8F5FDE62}"/>
   </bookViews>
   <sheets>
     <sheet name="Subsidy_short" sheetId="4" r:id="rId1"/>
@@ -1475,22 +1475,22 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="C3">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="D3">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="E3">
-        <v>1.1299999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="F3">
-        <v>1.1599999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="G3">
-        <v>1.1200000000000001</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -1498,22 +1498,22 @@
         <v>2030</v>
       </c>
       <c r="B4">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="C4">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="D4">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="E4">
-        <v>1.1299999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="F4">
-        <v>1.1599999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="G4">
-        <v>1.1200000000000001</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1521,22 +1521,22 @@
         <v>2035</v>
       </c>
       <c r="B5">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="C5">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="D5">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="E5">
-        <v>1.1299999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="F5">
-        <v>1.1599999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="G5">
-        <v>1.1200000000000001</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -1544,22 +1544,22 @@
         <v>2040</v>
       </c>
       <c r="B6">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="C6">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="D6">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="E6">
-        <v>1.1299999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="F6">
-        <v>1.1599999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="G6">
-        <v>1.1200000000000001</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -1567,22 +1567,22 @@
         <v>2045</v>
       </c>
       <c r="B7">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="C7">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="D7">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="E7">
-        <v>1.1299999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="F7">
-        <v>1.1599999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="G7">
-        <v>1.1200000000000001</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -1590,22 +1590,22 @@
         <v>2050</v>
       </c>
       <c r="B8">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="C8">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="D8">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="E8">
-        <v>1.1299999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="F8">
-        <v>1.1599999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="G8">
-        <v>1.1200000000000001</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>

--- a/technology.xlsx
+++ b/technology.xlsx
@@ -1,27 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hy4174/Documents/GitHub/GCAM_USA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F7E3D4-4064-3B47-98BC-4FD8A68C33D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394E68DC-4698-5148-829C-B904F4EBDEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26880" yWindow="4400" windowWidth="24320" windowHeight="20520" activeTab="5" xr2:uid="{05EA3646-A85E-534D-A1FC-571F8F5FDE62}"/>
+    <workbookView xWindow="13000" yWindow="760" windowWidth="34560" windowHeight="20460" firstSheet="3" activeTab="8" xr2:uid="{05EA3646-A85E-534D-A1FC-571F8F5FDE62}"/>
   </bookViews>
   <sheets>
     <sheet name="Subsidy_short" sheetId="4" r:id="rId1"/>
-    <sheet name="Subsidy_long" sheetId="1" r:id="rId2"/>
+    <sheet name="Subsidy" sheetId="1" r:id="rId2"/>
     <sheet name="Tariff_short" sheetId="5" r:id="rId3"/>
-    <sheet name="Tariff_long" sheetId="2" r:id="rId4"/>
+    <sheet name="Tariff_wide" sheetId="2" r:id="rId4"/>
     <sheet name="Tariff_current" sheetId="6" r:id="rId5"/>
-    <sheet name="Tariff_shock" sheetId="7" r:id="rId6"/>
-    <sheet name="Tariff_chaos" sheetId="8" r:id="rId7"/>
-    <sheet name="Wind" sheetId="9" r:id="rId8"/>
-    <sheet name="Free" sheetId="3" r:id="rId9"/>
+    <sheet name="Tariff_chaos" sheetId="8" r:id="rId6"/>
+    <sheet name="Onshore_supply" sheetId="10" r:id="rId7"/>
+    <sheet name="Onshore" sheetId="12" r:id="rId8"/>
+    <sheet name="Onshore_random" sheetId="13" r:id="rId9"/>
+    <sheet name="Onshore_chaos" sheetId="7" r:id="rId10"/>
+    <sheet name="Free" sheetId="3" r:id="rId11"/>
+    <sheet name="REF_chaos" sheetId="11" r:id="rId12"/>
+    <sheet name="Wind" sheetId="9" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="12">
   <si>
     <t>PV_int</t>
   </si>
@@ -643,6 +647,854 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82AEDC6-D0F2-314D-BC89-A31579160FFD}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2020</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <f>1.88*2.5</f>
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:D4" si="0">1.88*2.5</f>
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="E3">
+        <f>2.5*1.64</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2030</v>
+      </c>
+      <c r="B4">
+        <f>1.88*2.5</f>
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>4.6999999999999993</v>
+      </c>
+      <c r="E4">
+        <f>2.5*1.64</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F4">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2035</v>
+      </c>
+      <c r="B5">
+        <f>2.5*1.13</f>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:D8" si="1">2.5*1.13</f>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="E5">
+        <f>2.5*1.12</f>
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="F5">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2040</v>
+      </c>
+      <c r="B6">
+        <f t="shared" ref="B6:B8" si="2">2.5*1.13</f>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ref="E6:E8" si="3">2.5*1.12</f>
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="F6">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2045</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="2"/>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="3"/>
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="F7">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2050</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="2"/>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>2.8249999999999997</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="3"/>
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="F8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3D3ACA-D2F4-F244-9F9C-304236E3C5E6}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2020</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>0.86</v>
+      </c>
+      <c r="C3">
+        <v>0.86</v>
+      </c>
+      <c r="D3">
+        <v>0.86</v>
+      </c>
+      <c r="E3">
+        <v>0.9</v>
+      </c>
+      <c r="F3">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2030</v>
+      </c>
+      <c r="B4">
+        <v>0.86</v>
+      </c>
+      <c r="C4">
+        <v>0.86</v>
+      </c>
+      <c r="D4">
+        <v>0.86</v>
+      </c>
+      <c r="E4">
+        <v>0.9</v>
+      </c>
+      <c r="F4">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2035</v>
+      </c>
+      <c r="B5">
+        <v>0.86</v>
+      </c>
+      <c r="C5">
+        <v>0.86</v>
+      </c>
+      <c r="D5">
+        <v>0.86</v>
+      </c>
+      <c r="E5">
+        <v>0.9</v>
+      </c>
+      <c r="F5">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2040</v>
+      </c>
+      <c r="B6">
+        <v>0.86</v>
+      </c>
+      <c r="C6">
+        <v>0.86</v>
+      </c>
+      <c r="D6">
+        <v>0.86</v>
+      </c>
+      <c r="E6">
+        <v>0.9</v>
+      </c>
+      <c r="F6">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2045</v>
+      </c>
+      <c r="B7">
+        <v>0.86</v>
+      </c>
+      <c r="C7">
+        <v>0.86</v>
+      </c>
+      <c r="D7">
+        <v>0.86</v>
+      </c>
+      <c r="E7">
+        <v>0.9</v>
+      </c>
+      <c r="F7">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2050</v>
+      </c>
+      <c r="B8">
+        <v>0.86</v>
+      </c>
+      <c r="C8">
+        <v>0.86</v>
+      </c>
+      <c r="D8">
+        <v>0.86</v>
+      </c>
+      <c r="E8">
+        <v>0.9</v>
+      </c>
+      <c r="F8">
+        <v>0.47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D24B6777-83F4-0E40-A8C2-493F42A09BC8}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2020</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>2.5</v>
+      </c>
+      <c r="C3">
+        <v>2.5</v>
+      </c>
+      <c r="D3">
+        <v>2.5</v>
+      </c>
+      <c r="E3">
+        <v>2.5</v>
+      </c>
+      <c r="F3">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2030</v>
+      </c>
+      <c r="B4">
+        <v>2.5</v>
+      </c>
+      <c r="C4">
+        <v>2.5</v>
+      </c>
+      <c r="D4">
+        <v>2.5</v>
+      </c>
+      <c r="E4">
+        <v>2.5</v>
+      </c>
+      <c r="F4">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2035</v>
+      </c>
+      <c r="B5">
+        <v>2.5</v>
+      </c>
+      <c r="C5">
+        <v>2.5</v>
+      </c>
+      <c r="D5">
+        <v>2.5</v>
+      </c>
+      <c r="E5">
+        <v>2.5</v>
+      </c>
+      <c r="F5">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2040</v>
+      </c>
+      <c r="B6">
+        <v>2.5</v>
+      </c>
+      <c r="C6">
+        <v>2.5</v>
+      </c>
+      <c r="D6">
+        <v>2.5</v>
+      </c>
+      <c r="E6">
+        <v>2.5</v>
+      </c>
+      <c r="F6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2045</v>
+      </c>
+      <c r="B7">
+        <v>2.5</v>
+      </c>
+      <c r="C7">
+        <v>2.5</v>
+      </c>
+      <c r="D7">
+        <v>2.5</v>
+      </c>
+      <c r="E7">
+        <v>2.5</v>
+      </c>
+      <c r="F7">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2050</v>
+      </c>
+      <c r="B8">
+        <v>2.5</v>
+      </c>
+      <c r="C8">
+        <v>2.5</v>
+      </c>
+      <c r="D8">
+        <v>2.5</v>
+      </c>
+      <c r="E8">
+        <v>2.5</v>
+      </c>
+      <c r="F8">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE15934-C73C-2847-800F-1BF3FABA10B6}">
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2020</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>1.5</v>
+      </c>
+      <c r="C3">
+        <v>1.5</v>
+      </c>
+      <c r="D3">
+        <v>1.5</v>
+      </c>
+      <c r="E3">
+        <v>1.5</v>
+      </c>
+      <c r="F3">
+        <v>1.5</v>
+      </c>
+      <c r="G3">
+        <v>1.25</v>
+      </c>
+      <c r="H3">
+        <v>1.25</v>
+      </c>
+      <c r="I3">
+        <v>1.25</v>
+      </c>
+      <c r="J3">
+        <v>1.25</v>
+      </c>
+      <c r="K3">
+        <v>1.25</v>
+      </c>
+      <c r="L3">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2030</v>
+      </c>
+      <c r="B4">
+        <v>1.5</v>
+      </c>
+      <c r="C4">
+        <v>1.5</v>
+      </c>
+      <c r="D4">
+        <v>1.5</v>
+      </c>
+      <c r="E4">
+        <v>1.5</v>
+      </c>
+      <c r="F4">
+        <v>1.5</v>
+      </c>
+      <c r="G4">
+        <v>1.25</v>
+      </c>
+      <c r="H4">
+        <v>1.25</v>
+      </c>
+      <c r="I4">
+        <v>1.25</v>
+      </c>
+      <c r="J4">
+        <v>1.25</v>
+      </c>
+      <c r="K4">
+        <v>1.25</v>
+      </c>
+      <c r="L4">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2035</v>
+      </c>
+      <c r="B5">
+        <v>1.5</v>
+      </c>
+      <c r="C5">
+        <v>1.5</v>
+      </c>
+      <c r="D5">
+        <v>1.5</v>
+      </c>
+      <c r="E5">
+        <v>1.5</v>
+      </c>
+      <c r="F5">
+        <v>1.5</v>
+      </c>
+      <c r="G5">
+        <v>1.25</v>
+      </c>
+      <c r="H5">
+        <v>1.25</v>
+      </c>
+      <c r="I5">
+        <v>1.25</v>
+      </c>
+      <c r="J5">
+        <v>1.25</v>
+      </c>
+      <c r="K5">
+        <v>1.25</v>
+      </c>
+      <c r="L5">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2040</v>
+      </c>
+      <c r="B6">
+        <v>1.5</v>
+      </c>
+      <c r="C6">
+        <v>1.5</v>
+      </c>
+      <c r="D6">
+        <v>1.5</v>
+      </c>
+      <c r="E6">
+        <v>1.5</v>
+      </c>
+      <c r="F6">
+        <v>1.5</v>
+      </c>
+      <c r="G6">
+        <v>1.25</v>
+      </c>
+      <c r="H6">
+        <v>1.25</v>
+      </c>
+      <c r="I6">
+        <v>1.25</v>
+      </c>
+      <c r="J6">
+        <v>1.25</v>
+      </c>
+      <c r="K6">
+        <v>1.25</v>
+      </c>
+      <c r="L6">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2045</v>
+      </c>
+      <c r="B7">
+        <v>1.5</v>
+      </c>
+      <c r="C7">
+        <v>1.5</v>
+      </c>
+      <c r="D7">
+        <v>1.5</v>
+      </c>
+      <c r="E7">
+        <v>1.5</v>
+      </c>
+      <c r="F7">
+        <v>1.5</v>
+      </c>
+      <c r="G7">
+        <v>1.25</v>
+      </c>
+      <c r="H7">
+        <v>1.25</v>
+      </c>
+      <c r="I7">
+        <v>1.25</v>
+      </c>
+      <c r="J7">
+        <v>1.25</v>
+      </c>
+      <c r="K7">
+        <v>1.25</v>
+      </c>
+      <c r="L7">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2050</v>
+      </c>
+      <c r="B8">
+        <v>1.5</v>
+      </c>
+      <c r="C8">
+        <v>1.5</v>
+      </c>
+      <c r="D8">
+        <v>1.5</v>
+      </c>
+      <c r="E8">
+        <v>1.5</v>
+      </c>
+      <c r="F8">
+        <v>1.5</v>
+      </c>
+      <c r="G8">
+        <v>1.25</v>
+      </c>
+      <c r="H8">
+        <v>1.25</v>
+      </c>
+      <c r="I8">
+        <v>1.25</v>
+      </c>
+      <c r="J8">
+        <v>1.25</v>
+      </c>
+      <c r="K8">
+        <v>1.25</v>
+      </c>
+      <c r="L8">
+        <v>1.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF65D085-11C0-2648-9DC0-22E5F6B2E8BA}">
   <dimension ref="A1:G8"/>
@@ -699,22 +1551,22 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="C3">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="D3">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="E3">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="F3">
-        <v>0.94</v>
+        <v>0.7</v>
       </c>
       <c r="G3">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -722,22 +1574,22 @@
         <v>2030</v>
       </c>
       <c r="B4">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="C4">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="D4">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="E4">
-        <v>0.94</v>
+        <v>0.7</v>
       </c>
       <c r="F4">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="G4">
-        <v>0.73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -745,22 +1597,22 @@
         <v>2035</v>
       </c>
       <c r="B5">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="C5">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="D5">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="E5">
-        <v>0.94</v>
+        <v>0.7</v>
       </c>
       <c r="F5">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="G5">
-        <v>0.73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -768,22 +1620,22 @@
         <v>2040</v>
       </c>
       <c r="B6">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="C6">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="D6">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="E6">
-        <v>0.94</v>
+        <v>0.7</v>
       </c>
       <c r="F6">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="G6">
-        <v>0.73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -791,22 +1643,22 @@
         <v>2045</v>
       </c>
       <c r="B7">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="C7">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="D7">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="E7">
-        <v>0.94</v>
+        <v>0.7</v>
       </c>
       <c r="F7">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="G7">
-        <v>0.73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -814,22 +1666,22 @@
         <v>2050</v>
       </c>
       <c r="B8">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="C8">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="D8">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="E8">
-        <v>0.94</v>
+        <v>0.7</v>
       </c>
       <c r="F8">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="G8">
-        <v>0.73</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1087,22 +1939,22 @@
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="C3">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="D3">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="E3">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="F3">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="G3">
-        <v>1.06</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -1110,22 +1962,22 @@
         <v>2030</v>
       </c>
       <c r="B4">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="C4">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="D4">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="E4">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="F4">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="G4">
-        <v>1.06</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1133,22 +1985,22 @@
         <v>2035</v>
       </c>
       <c r="B5">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="C5">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="D5">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="E5">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="F5">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="G5">
-        <v>1.06</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -1156,22 +2008,22 @@
         <v>2040</v>
       </c>
       <c r="B6">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="C6">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="D6">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="E6">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="F6">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="G6">
-        <v>1.06</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -1179,22 +2031,22 @@
         <v>2045</v>
       </c>
       <c r="B7">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="C7">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="D7">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="E7">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="F7">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="G7">
-        <v>1.06</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -1202,22 +2054,22 @@
         <v>2050</v>
       </c>
       <c r="B8">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="C8">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="D8">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="E8">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="F8">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="G8">
-        <v>1.06</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1227,10 +2079,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5710655-89B8-B74B-84FF-D2C3A3CD63F0}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1247,13 +2099,10 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -1272,11 +2121,8 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1290,16 +2136,13 @@
         <v>1.24</v>
       </c>
       <c r="E3">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F3">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="G3">
         <v>1.02</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2030</v>
       </c>
@@ -1313,16 +2156,13 @@
         <v>1.24</v>
       </c>
       <c r="E4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F4">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="G4">
         <v>1.02</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2035</v>
       </c>
@@ -1336,16 +2176,13 @@
         <v>1.24</v>
       </c>
       <c r="E5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F5">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="G5">
         <v>1.02</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2040</v>
       </c>
@@ -1359,16 +2196,13 @@
         <v>1.24</v>
       </c>
       <c r="E6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F6">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="G6">
         <v>1.02</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2045</v>
       </c>
@@ -1382,16 +2216,13 @@
         <v>1.24</v>
       </c>
       <c r="E7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F7">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="G7">
         <v>1.02</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2050</v>
       </c>
@@ -1405,12 +2236,9 @@
         <v>1.24</v>
       </c>
       <c r="E8">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F8">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="G8">
         <v>1.02</v>
       </c>
     </row>
@@ -1420,11 +2248,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82AEDC6-D0F2-314D-BC89-A31579160FFD}">
-  <dimension ref="A1:G8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C2BFAC9-78FC-BF4A-99A8-36F6CB12AAB4}">
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1441,13 +2269,10 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -1466,146 +2291,149 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>1.38</v>
+        <f>1.24*2.5</f>
+        <v>3.1</v>
       </c>
       <c r="C3">
-        <v>1.38</v>
+        <f t="shared" ref="C3:D8" si="0">1.24*2.5</f>
+        <v>3.1</v>
       </c>
       <c r="D3">
-        <v>1.38</v>
+        <f t="shared" si="0"/>
+        <v>3.1</v>
       </c>
       <c r="E3">
-        <v>1.25</v>
+        <f>1.19*2.5</f>
+        <v>2.9749999999999996</v>
       </c>
       <c r="F3">
-        <v>1.44</v>
-      </c>
-      <c r="G3">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2030</v>
       </c>
       <c r="B4">
-        <v>1.38</v>
+        <f t="shared" ref="B4:B8" si="1">1.24*2.5</f>
+        <v>3.1</v>
       </c>
       <c r="C4">
-        <v>1.38</v>
+        <f t="shared" si="0"/>
+        <v>3.1</v>
       </c>
       <c r="D4">
-        <v>1.38</v>
+        <f t="shared" si="0"/>
+        <v>3.1</v>
       </c>
       <c r="E4">
-        <v>1.25</v>
+        <f t="shared" ref="E4:E8" si="2">1.19*2.5</f>
+        <v>2.9749999999999996</v>
       </c>
       <c r="F4">
-        <v>1.44</v>
-      </c>
-      <c r="G4">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2035</v>
       </c>
       <c r="B5">
-        <v>1.38</v>
+        <f t="shared" si="1"/>
+        <v>3.1</v>
       </c>
       <c r="C5">
-        <v>1.38</v>
+        <f t="shared" si="0"/>
+        <v>3.1</v>
       </c>
       <c r="D5">
-        <v>1.38</v>
+        <f t="shared" si="0"/>
+        <v>3.1</v>
       </c>
       <c r="E5">
-        <v>1.25</v>
+        <f t="shared" si="2"/>
+        <v>2.9749999999999996</v>
       </c>
       <c r="F5">
-        <v>1.44</v>
-      </c>
-      <c r="G5">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2040</v>
       </c>
       <c r="B6">
-        <v>1.38</v>
+        <f t="shared" si="1"/>
+        <v>3.1</v>
       </c>
       <c r="C6">
-        <v>1.38</v>
+        <f t="shared" si="0"/>
+        <v>3.1</v>
       </c>
       <c r="D6">
-        <v>1.38</v>
+        <f t="shared" si="0"/>
+        <v>3.1</v>
       </c>
       <c r="E6">
-        <v>1.25</v>
+        <f t="shared" si="2"/>
+        <v>2.9749999999999996</v>
       </c>
       <c r="F6">
-        <v>1.44</v>
-      </c>
-      <c r="G6">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2045</v>
       </c>
       <c r="B7">
-        <v>1.38</v>
+        <f t="shared" si="1"/>
+        <v>3.1</v>
       </c>
       <c r="C7">
-        <v>1.38</v>
+        <f t="shared" si="0"/>
+        <v>3.1</v>
       </c>
       <c r="D7">
-        <v>1.38</v>
+        <f t="shared" si="0"/>
+        <v>3.1</v>
       </c>
       <c r="E7">
-        <v>1.25</v>
+        <f t="shared" si="2"/>
+        <v>2.9749999999999996</v>
       </c>
       <c r="F7">
-        <v>1.44</v>
-      </c>
-      <c r="G7">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2050</v>
       </c>
       <c r="B8">
-        <v>1.38</v>
+        <f t="shared" si="1"/>
+        <v>3.1</v>
       </c>
       <c r="C8">
-        <v>1.38</v>
+        <f t="shared" si="0"/>
+        <v>3.1</v>
       </c>
       <c r="D8">
-        <v>1.38</v>
+        <f t="shared" si="0"/>
+        <v>3.1</v>
       </c>
       <c r="E8">
-        <v>1.25</v>
+        <f t="shared" si="2"/>
+        <v>2.9749999999999996</v>
       </c>
       <c r="F8">
-        <v>1.44</v>
-      </c>
-      <c r="G8">
-        <v>1.7</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1614,11 +2442,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C2BFAC9-78FC-BF4A-99A8-36F6CB12AAB4}">
-  <dimension ref="A1:G8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91E8B155-4D47-3B4E-9CF0-F16174517601}">
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1635,13 +2463,10 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -1660,146 +2485,125 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="C3">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="D3">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="E3">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="F3">
-        <v>1.5</v>
-      </c>
-      <c r="G3">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2030</v>
       </c>
       <c r="B4">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="C4">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="D4">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="E4">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="F4">
-        <v>1.5</v>
-      </c>
-      <c r="G4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2035</v>
       </c>
       <c r="B5">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C5">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D5">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E5">
-        <v>1.5</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F5">
-        <v>1.5</v>
-      </c>
-      <c r="G5">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2040</v>
       </c>
       <c r="B6">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C6">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D6">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E6">
-        <v>1.5</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F6">
-        <v>1.5</v>
-      </c>
-      <c r="G6">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2045</v>
       </c>
       <c r="B7">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C7">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D7">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E7">
-        <v>1.5</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F7">
-        <v>1.5</v>
-      </c>
-      <c r="G7">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2050</v>
       </c>
       <c r="B8">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D8">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E8">
-        <v>1.5</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F8">
-        <v>1.5</v>
-      </c>
-      <c r="G8">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
     </row>
   </sheetData>
@@ -1808,11 +2612,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE15934-C73C-2847-800F-1BF3FABA10B6}">
-  <dimension ref="A1:L8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD6410A-285A-1B4D-AD90-6A600564CCDB}">
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -1829,28 +2633,10 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -1869,251 +2655,125 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C3">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D3">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E3">
-        <v>1.5</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F3">
-        <v>1.5</v>
-      </c>
-      <c r="G3">
-        <v>1.25</v>
-      </c>
-      <c r="H3">
-        <v>1.25</v>
-      </c>
-      <c r="I3">
-        <v>1.25</v>
-      </c>
-      <c r="J3">
-        <v>1.25</v>
-      </c>
-      <c r="K3">
-        <v>1.25</v>
-      </c>
-      <c r="L3">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2030</v>
       </c>
       <c r="B4">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C4">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D4">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E4">
-        <v>1.5</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F4">
-        <v>1.5</v>
-      </c>
-      <c r="G4">
-        <v>1.25</v>
-      </c>
-      <c r="H4">
-        <v>1.25</v>
-      </c>
-      <c r="I4">
-        <v>1.25</v>
-      </c>
-      <c r="J4">
-        <v>1.25</v>
-      </c>
-      <c r="K4">
-        <v>1.25</v>
-      </c>
-      <c r="L4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2035</v>
       </c>
       <c r="B5">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C5">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D5">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E5">
-        <v>1.5</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F5">
-        <v>1.5</v>
-      </c>
-      <c r="G5">
-        <v>1.25</v>
-      </c>
-      <c r="H5">
-        <v>1.25</v>
-      </c>
-      <c r="I5">
-        <v>1.25</v>
-      </c>
-      <c r="J5">
-        <v>1.25</v>
-      </c>
-      <c r="K5">
-        <v>1.25</v>
-      </c>
-      <c r="L5">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2040</v>
       </c>
       <c r="B6">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C6">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D6">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E6">
-        <v>1.5</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F6">
-        <v>1.5</v>
-      </c>
-      <c r="G6">
-        <v>1.25</v>
-      </c>
-      <c r="H6">
-        <v>1.25</v>
-      </c>
-      <c r="I6">
-        <v>1.25</v>
-      </c>
-      <c r="J6">
-        <v>1.25</v>
-      </c>
-      <c r="K6">
-        <v>1.25</v>
-      </c>
-      <c r="L6">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2045</v>
       </c>
       <c r="B7">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C7">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D7">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E7">
-        <v>1.5</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F7">
-        <v>1.5</v>
-      </c>
-      <c r="G7">
-        <v>1.25</v>
-      </c>
-      <c r="H7">
-        <v>1.25</v>
-      </c>
-      <c r="I7">
-        <v>1.25</v>
-      </c>
-      <c r="J7">
-        <v>1.25</v>
-      </c>
-      <c r="K7">
-        <v>1.25</v>
-      </c>
-      <c r="L7">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2050</v>
       </c>
       <c r="B8">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D8">
-        <v>1.5</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E8">
-        <v>1.5</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F8">
-        <v>1.5</v>
-      </c>
-      <c r="G8">
-        <v>1.25</v>
-      </c>
-      <c r="H8">
-        <v>1.25</v>
-      </c>
-      <c r="I8">
-        <v>1.25</v>
-      </c>
-      <c r="J8">
-        <v>1.25</v>
-      </c>
-      <c r="K8">
-        <v>1.25</v>
-      </c>
-      <c r="L8">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
     </row>
   </sheetData>
@@ -2122,11 +2782,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3D3ACA-D2F4-F244-9F9C-304236E3C5E6}">
-  <dimension ref="A1:G8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5557D4F2-9532-AC4B-A31E-1A61DED13C1B}">
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2143,13 +2803,10 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2020</v>
       </c>
@@ -2168,146 +2825,125 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2025</v>
       </c>
       <c r="B3">
-        <v>0.87</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>0.87</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>0.87</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>0.92</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0.91</v>
-      </c>
-      <c r="G3">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2030</v>
       </c>
       <c r="B4">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C4">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D4">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E4">
-        <v>0.92</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F4">
-        <v>0.91</v>
-      </c>
-      <c r="G4">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2035</v>
       </c>
       <c r="B5">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C5">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D5">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E5">
-        <v>0.92</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F5">
-        <v>0.91</v>
-      </c>
-      <c r="G5">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2040</v>
       </c>
       <c r="B6">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C6">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D6">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E6">
-        <v>0.92</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F6">
-        <v>0.91</v>
-      </c>
-      <c r="G6">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2045</v>
       </c>
       <c r="B7">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C7">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D7">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E7">
-        <v>0.92</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F7">
-        <v>0.91</v>
-      </c>
-      <c r="G7">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2050</v>
       </c>
       <c r="B8">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="C8">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="D8">
-        <v>0.87</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="E8">
-        <v>0.92</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F8">
-        <v>0.91</v>
-      </c>
-      <c r="G8">
-        <v>0.71</v>
+        <v>1.06</v>
       </c>
     </row>
   </sheetData>
